--- a/data/trans_orig/P2A_psíq_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11902</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>467550</t>
+          <t>467654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295363</t>
+          <t>294778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304754</t>
+          <t>304753</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>765503</t>
+          <t>765919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>777267</t>
+          <t>777276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13742</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356634</t>
+          <t>357126</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366121</t>
+          <t>366108</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>364045</t>
+          <t>362934</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370933</t>
+          <t>370926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>725057</t>
+          <t>725195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736261</t>
+          <t>736785</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534319</t>
+          <t>534673</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541480</t>
+          <t>541478</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160996</t>
+          <t>160990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>699680</t>
+          <t>699321</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>708300</t>
+          <t>708258</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20673</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14271</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32041</t>
+          <t>34040</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1217661</t>
+          <t>1217338</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1231966</t>
+          <t>1231915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>696330</t>
+          <t>695549</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>709267</t>
+          <t>709160</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1920579</t>
+          <t>1918580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1938349</t>
+          <t>1939384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>342270</t>
+          <t>343319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>349735</t>
+          <t>350555</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>559138</t>
+          <t>559065</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>907341</t>
+          <t>906606</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>917041</t>
+          <t>916739</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13815</t>
+          <t>14637</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>26892</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14953</t>
+          <t>14671</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34786</t>
+          <t>33879</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284386</t>
+          <t>283564</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295562</t>
+          <t>295968</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1222899</t>
+          <t>1221868</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1239946</t>
+          <t>1239447</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1512174</t>
+          <t>1513081</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1532007</t>
+          <t>1532289</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20339</t>
+          <t>20049</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42908</t>
+          <t>44031</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28003</t>
+          <t>28013</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54426</t>
+          <t>53119</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54551</t>
+          <t>53805</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87263</t>
+          <t>86878</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3227282</t>
+          <t>3226159</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3249851</t>
+          <t>3250141</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,82 +2919,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3257</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3338648</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3325005</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3350111</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>6436</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6579098</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6561436</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6594509</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3257</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3338648</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3323698</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3350121</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>6436</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6579098</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6561051</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6593763</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>22038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>425288</t>
+          <t>426182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435132</t>
+          <t>435176</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297887</t>
+          <t>298270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311261</t>
+          <t>311359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730085</t>
+          <t>729627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744633</t>
+          <t>744689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19849</t>
+          <t>22364</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22489</t>
+          <t>23852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398948</t>
+          <t>396433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414606</t>
+          <t>414698</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331655</t>
+          <t>330570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>734319</t>
+          <t>732956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>750756</t>
+          <t>750922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9237</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29163</t>
+          <t>29483</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31568</t>
+          <t>32612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>600252</t>
+          <t>599932</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620178</t>
+          <t>619896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>252172</t>
+          <t>251316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259196</t>
+          <t>259185</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>857976</t>
+          <t>856932</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878069</t>
+          <t>877982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>21652</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28193</t>
+          <t>29031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45507</t>
+          <t>44336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1134833</t>
+          <t>1137357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1151000</t>
+          <t>1151876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>738464</t>
+          <t>737626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>755812</t>
+          <t>755806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1880160</t>
+          <t>1881331</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1903478</t>
+          <t>1904438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14179</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33850</t>
+          <t>34567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41677</t>
+          <t>41290</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>496712</t>
+          <t>496601</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507613</t>
+          <t>507622</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>727672</t>
+          <t>726955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>747343</t>
+          <t>746807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1230441</t>
+          <t>1230828</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1252678</t>
+          <t>1251918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32260</t>
+          <t>32823</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>21900</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46035</t>
+          <t>47611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247320</t>
+          <t>246394</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261943</t>
+          <t>261801</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1077091</t>
+          <t>1076528</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1096480</t>
+          <t>1095379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1330198</t>
+          <t>1328622</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1354080</t>
+          <t>1354333</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48357</t>
+          <t>48389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83350</t>
+          <t>82285</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58073</t>
+          <t>58304</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96167</t>
+          <t>92849</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>115392</t>
+          <t>114187</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164530</t>
+          <t>162529</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3338560</t>
+          <t>3339625</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3373553</t>
+          <t>3373521</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3453958</t>
+          <t>3457276</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3492052</t>
+          <t>3491821</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6807505</t>
+          <t>6809506</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6856643</t>
+          <t>6857848</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>11329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423953</t>
+          <t>423631</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>338744</t>
+          <t>337629</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>346060</t>
+          <t>346067</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>765370</t>
+          <t>764818</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>774943</t>
+          <t>774933</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10961</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18989</t>
+          <t>18041</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366266</t>
+          <t>366936</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376336</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359148</t>
+          <t>357974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370309</t>
+          <t>370266</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730511</t>
+          <t>731459</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745506</t>
+          <t>745666</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>996</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11108</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512189</t>
+          <t>512259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520913</t>
+          <t>520918</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160791</t>
+          <t>160676</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>676928</t>
+          <t>677334</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686127</t>
+          <t>686200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21064</t>
+          <t>20434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28639</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1136174</t>
+          <t>1136176</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1146818</t>
+          <t>1146739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>804812</t>
+          <t>805442</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>818929</t>
+          <t>818979</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1946875</t>
+          <t>1946965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1963688</t>
+          <t>1964254</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31723</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>21650</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47244</t>
+          <t>46870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>600059</t>
+          <t>600594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>614665</t>
+          <t>615138</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>706521</t>
+          <t>706852</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>725986</t>
+          <t>726323</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1311706</t>
+          <t>1312080</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1336528</t>
+          <t>1337300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7978</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24739</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30421</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>275557</t>
+          <t>275485</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285186</t>
+          <t>285195</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1057286</t>
+          <t>1055965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1073890</t>
+          <t>1074047</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1338749</t>
+          <t>1338267</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1357615</t>
+          <t>1356795</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20916</t>
+          <t>21104</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45716</t>
+          <t>44675</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42674</t>
+          <t>43997</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>75424</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70925</t>
+          <t>70909</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108298</t>
+          <t>110291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3340006</t>
+          <t>3341047</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3364806</t>
+          <t>3364618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3455894</t>
+          <t>3456172</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3488922</t>
+          <t>3487599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6809020</t>
+          <t>6807027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6846393</t>
+          <t>6846409</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19824</t>
+          <t>20790</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20663</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15224</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34837</t>
+          <t>34214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485388</t>
+          <t>484422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498867</t>
+          <t>498766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>426804</t>
+          <t>427204</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>441184</t>
+          <t>440616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>917842</t>
+          <t>918465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>937455</t>
+          <t>937724</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15426</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24658</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>436908</t>
+          <t>436787</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448751</t>
+          <t>448631</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368676</t>
+          <t>368476</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>377513</t>
+          <t>377408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>810135</t>
+          <t>810031</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>823876</t>
+          <t>823878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>17156</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>651070</t>
+          <t>651108</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666162</t>
+          <t>666379</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159676</t>
+          <t>159951</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165726</t>
+          <t>165741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>814218</t>
+          <t>814295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>831466</t>
+          <t>831534</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13292</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30058</t>
+          <t>30383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21120</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>585908</t>
+          <t>517339</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>40187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>754498</t>
+          <t>821809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1004761</t>
+          <t>1004436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1021527</t>
+          <t>1021501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>392186</t>
+          <t>460755</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>956974</t>
+          <t>957759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1258414</t>
+          <t>1191103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1973477</t>
+          <t>1972725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29697</t>
+          <t>30871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25838</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48135</t>
+          <t>47538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>453723</t>
+          <t>454554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467517</t>
+          <t>467959</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>811638</t>
+          <t>810464</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>826737</t>
+          <t>827109</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1268246</t>
+          <t>1268843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1290543</t>
+          <t>1291029</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>19276</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37910</t>
+          <t>37041</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24752</t>
+          <t>24203</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48585</t>
+          <t>46742</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221879</t>
+          <t>222815</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237840</t>
+          <t>237441</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>723461</t>
+          <t>724330</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>742222</t>
+          <t>742095</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>953293</t>
+          <t>955136</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>977126</t>
+          <t>977675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49553</t>
+          <t>49750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87545</t>
+          <t>87329</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92426</t>
+          <t>91441</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>908487</t>
+          <t>916920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>157509</t>
+          <t>156972</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1045243</t>
+          <t>1064040</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3288515</t>
+          <t>3288731</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3326507</t>
+          <t>3326310</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2669271</t>
+          <t>2660838</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3485332</t>
+          <t>3486317</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5908575</t>
+          <t>5889778</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6796309</t>
+          <t>6796846</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_psíq_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>14810</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>467654</t>
+          <t>466013</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294778</t>
+          <t>295209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304753</t>
+          <t>304668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>765919</t>
+          <t>765647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>777276</t>
+          <t>777320</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357126</t>
+          <t>356991</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366108</t>
+          <t>366107</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>362934</t>
+          <t>363363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370926</t>
+          <t>370932</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>725195</t>
+          <t>725786</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736785</t>
+          <t>736237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>915</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>10764</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534673</t>
+          <t>534348</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541478</t>
+          <t>541474</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160990</t>
+          <t>161045</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>699321</t>
+          <t>699407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>708258</t>
+          <t>708290</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20996</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>13214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34040</t>
+          <t>31870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1217338</t>
+          <t>1217265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1231915</t>
+          <t>1232223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>695549</t>
+          <t>696379</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>709160</t>
+          <t>709252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1918580</t>
+          <t>1920750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1939384</t>
+          <t>1939406</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>343319</t>
+          <t>342407</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>350555</t>
+          <t>349737</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>559065</t>
+          <t>560302</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>567855</t>
+          <t>567858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>906606</t>
+          <t>906562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>916739</t>
+          <t>917075</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33879</t>
+          <t>33956</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283564</t>
+          <t>283606</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295968</t>
+          <t>295182</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1221868</t>
+          <t>1222480</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1239447</t>
+          <t>1239500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1513081</t>
+          <t>1513004</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1532289</t>
+          <t>1533076</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20049</t>
+          <t>19308</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44031</t>
+          <t>43339</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28013</t>
+          <t>28023</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53119</t>
+          <t>52615</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53805</t>
+          <t>54699</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86878</t>
+          <t>89303</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3226159</t>
+          <t>3226851</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3250141</t>
+          <t>3250882</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3325005</t>
+          <t>3325509</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3350111</t>
+          <t>3350101</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6561436</t>
+          <t>6559011</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6594509</t>
+          <t>6593615</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>17483</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>21580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426182</t>
+          <t>425892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435176</t>
+          <t>435160</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298270</t>
+          <t>296971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311359</t>
+          <t>310668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>729627</t>
+          <t>730085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744689</t>
+          <t>745418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22364</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>23656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>396433</t>
+          <t>398001</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414698</t>
+          <t>414855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330570</t>
+          <t>330599</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>732956</t>
+          <t>733152</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>750922</t>
+          <t>751153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29483</t>
+          <t>28788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32612</t>
+          <t>32540</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>599932</t>
+          <t>600627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619896</t>
+          <t>620361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251316</t>
+          <t>253121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259185</t>
+          <t>259188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>856932</t>
+          <t>857004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>877982</t>
+          <t>877835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21652</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29031</t>
+          <t>29195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>21927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44336</t>
+          <t>45212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1137357</t>
+          <t>1135767</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1151876</t>
+          <t>1151191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>737626</t>
+          <t>737462</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>755806</t>
+          <t>755923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1881331</t>
+          <t>1880455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1904438</t>
+          <t>1903740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34567</t>
+          <t>32170</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41290</t>
+          <t>42030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>496601</t>
+          <t>497392</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507622</t>
+          <t>507653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>726955</t>
+          <t>729352</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746807</t>
+          <t>747734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1230828</t>
+          <t>1230088</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1251918</t>
+          <t>1251636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>21592</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32823</t>
+          <t>31413</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21900</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47611</t>
+          <t>46932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246394</t>
+          <t>245290</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261801</t>
+          <t>261623</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1076528</t>
+          <t>1077938</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1095379</t>
+          <t>1096247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1328622</t>
+          <t>1329301</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1354333</t>
+          <t>1353756</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48389</t>
+          <t>48686</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82285</t>
+          <t>83993</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58304</t>
+          <t>58557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92849</t>
+          <t>92714</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>114187</t>
+          <t>114919</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>162529</t>
+          <t>162791</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3339625</t>
+          <t>3337917</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3373521</t>
+          <t>3373224</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3457276</t>
+          <t>3457411</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3491821</t>
+          <t>3491568</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6809506</t>
+          <t>6809244</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6857848</t>
+          <t>6857116</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11329</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423631</t>
+          <t>422891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>337629</t>
+          <t>338137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>346067</t>
+          <t>346070</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>764818</t>
+          <t>765505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>774933</t>
+          <t>774949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14299</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366936</t>
+          <t>365843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376321</t>
+          <t>376315</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357974</t>
+          <t>358970</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370266</t>
+          <t>370291</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731459</t>
+          <t>730339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745666</t>
+          <t>745513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512259</t>
+          <t>512315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520918</t>
+          <t>520914</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160676</t>
+          <t>160614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>677334</t>
+          <t>677378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686200</t>
+          <t>686242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20434</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28549</t>
+          <t>29680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1136176</t>
+          <t>1137305</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1146739</t>
+          <t>1146803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>805442</t>
+          <t>805726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>818979</t>
+          <t>819324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1946965</t>
+          <t>1945834</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1964254</t>
+          <t>1963716</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>21653</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11921</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>32003</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21650</t>
+          <t>21128</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46870</t>
+          <t>45104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>600594</t>
+          <t>599053</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>615138</t>
+          <t>615338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>706852</t>
+          <t>706241</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>726323</t>
+          <t>725938</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1312080</t>
+          <t>1313846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1337300</t>
+          <t>1337822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26060</t>
+          <t>26569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30903</t>
+          <t>30594</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>275485</t>
+          <t>276257</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285195</t>
+          <t>285268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1055965</t>
+          <t>1055456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1074047</t>
+          <t>1073826</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1338267</t>
+          <t>1338576</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1356795</t>
+          <t>1357006</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21104</t>
+          <t>21443</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44675</t>
+          <t>47395</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43997</t>
+          <t>44172</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75424</t>
+          <t>76328</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70909</t>
+          <t>71436</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110291</t>
+          <t>111975</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3341047</t>
+          <t>3338327</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3364618</t>
+          <t>3364279</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3456172</t>
+          <t>3455268</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3487599</t>
+          <t>3487424</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6807027</t>
+          <t>6805343</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6846409</t>
+          <t>6845882</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20790</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11734</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,17 +8703,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23171</t>
+          <t>25256</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>16805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34214</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>493774</t>
+          <t>537409</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>484422</t>
+          <t>528793</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498766</t>
+          <t>543697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>435733</t>
+          <t>476363</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427204</t>
+          <t>468111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>440616</t>
+          <t>481449</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,17 +8816,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>929508</t>
+          <t>1013773</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>918465</t>
+          <t>1000735</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>937724</t>
+          <t>1022224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,22 +8976,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15426</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24762</t>
+          <t>26733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -9089,27 +9089,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>444630</t>
+          <t>475356</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>436787</t>
+          <t>468024</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448631</t>
+          <t>479371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>373577</t>
+          <t>412671</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368476</t>
+          <t>406680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>377408</t>
+          <t>416964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>818207</t>
+          <t>888028</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>810031</t>
+          <t>879622</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>823878</t>
+          <t>894749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>12032</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>19074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>659963</t>
+          <t>463013</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>651108</t>
+          <t>456063</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666379</t>
+          <t>467310</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>163709</t>
+          <t>184064</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159951</t>
+          <t>179801</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165741</t>
+          <t>186165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>823672</t>
+          <t>647077</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>814295</t>
+          <t>640035</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>831534</t>
+          <t>652503</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,22 +9662,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>21780</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30383</t>
+          <t>31270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>223863</t>
+          <t>21581</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20335</t>
+          <t>14656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>517339</t>
+          <t>31180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>244563</t>
+          <t>43361</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40187</t>
+          <t>32407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>821809</t>
+          <t>56514</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -9775,27 +9775,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1014119</t>
+          <t>1110063</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1004436</t>
+          <t>1100573</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1021501</t>
+          <t>1117210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>754231</t>
+          <t>839630</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>460755</t>
+          <t>830031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>957759</t>
+          <t>846555</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1768349</t>
+          <t>1949693</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1191103</t>
+          <t>1936540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1972725</t>
+          <t>1960647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,22 +10005,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>24134</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22248</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>32611</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>35110</t>
+          <t>39418</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47538</t>
+          <t>52547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -10118,27 +10118,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>462184</t>
+          <t>553266</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>454554</t>
+          <t>543830</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467959</t>
+          <t>559489</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>819087</t>
+          <t>806130</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>810464</t>
+          <t>798239</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>827109</t>
+          <t>813205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1281271</t>
+          <t>1359396</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1268843</t>
+          <t>1346267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1291029</t>
+          <t>1369091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17692</t>
+          <t>23303</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26962</t>
+          <t>30938</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19276</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37041</t>
+          <t>42735</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>34559</t>
+          <t>41868</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24203</t>
+          <t>29601</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>57212</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>232910</t>
+          <t>226298</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222815</t>
+          <t>213925</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237441</t>
+          <t>232284</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>734409</t>
+          <t>813343</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>724330</t>
+          <t>801546</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>742095</t>
+          <t>822072</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>967319</t>
+          <t>1039641</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>955136</t>
+          <t>1024297</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>977675</t>
+          <t>1051908</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>68481</t>
+          <t>77073</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49750</t>
+          <t>60710</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87329</t>
+          <t>96622</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>297011</t>
+          <t>103189</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91441</t>
+          <t>86677</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>916920</t>
+          <t>122575</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>365492</t>
+          <t>180262</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156972</t>
+          <t>156736</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1064040</t>
+          <t>207643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3307579</t>
+          <t>3365403</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3288731</t>
+          <t>3345854</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3326310</t>
+          <t>3381766</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3280747</t>
+          <t>3532204</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2660838</t>
+          <t>3512818</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3486317</t>
+          <t>3548716</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6588326</t>
+          <t>6897607</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5889778</t>
+          <t>6870226</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6796846</t>
+          <t>6921133</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_psíq_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
